--- a/КПП/Том СОТС КПП/Реестр документов о качестве СОТС КПП.xlsx
+++ b/КПП/Том СОТС КПП/Реестр документов о качестве СОТС КПП.xlsx
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Лицо, выполнившее работы: ООО «АльтЭн», ОГРН 1024000944098, ИНН 4025062969</t>
   </si>
   <si>
-    <t xml:space="preserve">Здание: КПП. Том ИД: СОТС — система охранной и тревожной сигнализации (СОТС). Рабочая документация 16/1/26-СОТС-Р. Исполнительная документация 16/1/26-ИД-КПП, лист 6; кабельный журнал 16/1/26-ИД-КПП.КЖ (раздел СОТС)</t>
+    <t xml:space="preserve">Здание: КПП. Том ИД: СОТС — система охранной и тревожной сигнализации (СОТС). Рабочая документация 16/1/26-СОТС-Р. Исполнительная документация 16/1/26-СОТС-ИД-КПП, лист 2; кабельный журнал 16/1/26-СОТС-ИД-КПП.КЖ; спецификация 16/1/26-СОТС-ИД-КПП.СО</t>
   </si>
   <si>
     <t xml:space="preserve">РЕЕСТР</t>
